--- a/hall/resources/sample/PassDetails.xlsx
+++ b/hall/resources/sample/PassDetails.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gamedoc\游戏配置表\Manage\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
@@ -27,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="170">
   <si>
     <t>ID</t>
   </si>
@@ -89,6 +94,9 @@
     <t>PremiumPaidRewards</t>
   </si>
   <si>
+    <t>12284_1</t>
+  </si>
+  <si>
     <t>签到1天</t>
   </si>
   <si>
@@ -101,6 +109,9 @@
     <t>1130002_1</t>
   </si>
   <si>
+    <t>12284_2</t>
+  </si>
+  <si>
     <t>签到2天</t>
   </si>
   <si>
@@ -113,6 +124,9 @@
     <t>1130002_2</t>
   </si>
   <si>
+    <t>12284_3</t>
+  </si>
+  <si>
     <t>签到3天</t>
   </si>
   <si>
@@ -125,6 +139,9 @@
     <t>1130002_3</t>
   </si>
   <si>
+    <t>12284_4</t>
+  </si>
+  <si>
     <t>签到4天</t>
   </si>
   <si>
@@ -137,6 +154,9 @@
     <t>1130002_4</t>
   </si>
   <si>
+    <t>12284_5</t>
+  </si>
+  <si>
     <t>签到5天</t>
   </si>
   <si>
@@ -149,6 +169,9 @@
     <t>1130002_5</t>
   </si>
   <si>
+    <t>12284_6</t>
+  </si>
+  <si>
     <t>签到6天</t>
   </si>
   <si>
@@ -161,6 +184,9 @@
     <t>1130002_6</t>
   </si>
   <si>
+    <t>12284_7</t>
+  </si>
+  <si>
     <t>签到7天</t>
   </si>
   <si>
@@ -173,6 +199,9 @@
     <t>1130002_7</t>
   </si>
   <si>
+    <t>12284_8</t>
+  </si>
+  <si>
     <t>签到8天</t>
   </si>
   <si>
@@ -185,6 +214,9 @@
     <t>1130002_8</t>
   </si>
   <si>
+    <t>12284_9</t>
+  </si>
+  <si>
     <t>签到9天</t>
   </si>
   <si>
@@ -195,6 +227,9 @@
   </si>
   <si>
     <t>1130002_9</t>
+  </si>
+  <si>
+    <t>12284_10</t>
   </si>
   <si>
     <t>签到10天</t>
@@ -1783,21 +1818,23 @@
       <c r="C5" s="1">
         <v>1</v>
       </c>
-      <c r="D5" s="1"/>
+      <c r="D5" s="1" t="s">
+        <v>20</v>
+      </c>
       <c r="E5" s="1">
         <v>4061020</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" ht="16.5" spans="1:9">
@@ -1811,21 +1848,23 @@
       <c r="C6" s="1">
         <v>2</v>
       </c>
-      <c r="D6" s="1"/>
+      <c r="D6" s="1" t="s">
+        <v>25</v>
+      </c>
       <c r="E6" s="1">
         <v>4061020</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:9">
@@ -1839,21 +1878,23 @@
       <c r="C7" s="1">
         <v>3</v>
       </c>
-      <c r="D7" s="1"/>
+      <c r="D7" s="1" t="s">
+        <v>30</v>
+      </c>
       <c r="E7" s="1">
         <v>4061020</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8" ht="16.5" spans="1:9">
@@ -1867,21 +1908,23 @@
       <c r="C8" s="1">
         <v>4</v>
       </c>
-      <c r="D8" s="1"/>
+      <c r="D8" s="1" t="s">
+        <v>35</v>
+      </c>
       <c r="E8" s="1">
         <v>4061020</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9" ht="16.5" spans="1:9">
@@ -1895,21 +1938,23 @@
       <c r="C9" s="1">
         <v>5</v>
       </c>
-      <c r="D9" s="1"/>
+      <c r="D9" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="E9" s="1">
         <v>4061020</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10" ht="16.5" spans="1:9">
@@ -1923,21 +1968,23 @@
       <c r="C10" s="1">
         <v>6</v>
       </c>
-      <c r="D10" s="1"/>
+      <c r="D10" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="E10" s="1">
         <v>4061020</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="11" ht="16.5" spans="1:9">
@@ -1951,21 +1998,23 @@
       <c r="C11" s="1">
         <v>7</v>
       </c>
-      <c r="D11" s="1"/>
+      <c r="D11" s="1" t="s">
+        <v>50</v>
+      </c>
       <c r="E11" s="1">
         <v>4061020</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
     </row>
     <row r="12" ht="16.5" spans="1:9">
@@ -1979,21 +2028,23 @@
       <c r="C12" s="1">
         <v>8</v>
       </c>
-      <c r="D12" s="1"/>
+      <c r="D12" s="1" t="s">
+        <v>55</v>
+      </c>
       <c r="E12" s="1">
         <v>4061020</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
     </row>
     <row r="13" ht="16.5" spans="1:9">
@@ -2007,21 +2058,23 @@
       <c r="C13" s="1">
         <v>9</v>
       </c>
-      <c r="D13" s="1"/>
+      <c r="D13" s="1" t="s">
+        <v>60</v>
+      </c>
       <c r="E13" s="1">
         <v>4061020</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14" ht="16.5" spans="1:9">
@@ -2035,21 +2088,23 @@
       <c r="C14" s="1">
         <v>10</v>
       </c>
-      <c r="D14" s="1"/>
+      <c r="D14" s="1" t="s">
+        <v>65</v>
+      </c>
       <c r="E14" s="1">
         <v>4061020</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
     </row>
     <row r="15" ht="16.5" spans="1:9">
@@ -2064,22 +2119,22 @@
         <v>1</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="E15" s="3">
         <v>4061021</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="16" ht="16.5" spans="1:9">
@@ -2094,22 +2149,22 @@
         <v>2</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="E16" s="3">
         <v>4061021</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17" ht="16.5" spans="1:9">
@@ -2124,22 +2179,22 @@
         <v>3</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="E17" s="3">
         <v>4061021</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="18" ht="16.5" spans="1:9">
@@ -2154,22 +2209,22 @@
         <v>4</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="E18" s="3">
         <v>4061021</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19" ht="16.5" spans="1:9">
@@ -2184,22 +2239,22 @@
         <v>5</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="E19" s="3">
         <v>4061021</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="20" ht="16.5" spans="1:9">
@@ -2214,22 +2269,22 @@
         <v>6</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="E20" s="3">
         <v>4061021</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="1:9">
@@ -2244,22 +2299,22 @@
         <v>7</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="E21" s="3">
         <v>4061021</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
     </row>
     <row r="22" ht="16.5" spans="1:9">
@@ -2274,22 +2329,22 @@
         <v>8</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="E22" s="3">
         <v>4061021</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
     </row>
     <row r="23" ht="16.5" spans="1:9">
@@ -2304,22 +2359,22 @@
         <v>9</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="E23" s="3">
         <v>4061021</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
     </row>
     <row r="24" ht="16.5" spans="1:9">
@@ -2334,22 +2389,22 @@
         <v>10</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="E24" s="3">
         <v>4061021</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
     </row>
     <row r="25" ht="16.5" spans="1:9">
@@ -2364,22 +2419,22 @@
         <v>1</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="E25" s="1">
         <v>4061022</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="26" ht="16.5" spans="1:9">
@@ -2394,22 +2449,22 @@
         <v>2</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="E26" s="1">
         <v>4061022</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="27" ht="16.5" spans="1:9">
@@ -2424,22 +2479,22 @@
         <v>3</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="E27" s="1">
         <v>4061022</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="28" ht="16.5" spans="1:9">
@@ -2454,22 +2509,22 @@
         <v>4</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="E28" s="1">
         <v>4061022</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="29" ht="16.5" spans="1:9">
@@ -2484,22 +2539,22 @@
         <v>5</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="E29" s="1">
         <v>4061022</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="30" ht="16.5" spans="1:9">
@@ -2514,22 +2569,22 @@
         <v>6</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="E30" s="1">
         <v>4061022</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="31" ht="16.5" spans="1:9">
@@ -2544,22 +2599,22 @@
         <v>7</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="E31" s="1">
         <v>4061022</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
     </row>
     <row r="32" ht="16.5" spans="1:9">
@@ -2574,22 +2629,22 @@
         <v>8</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="E32" s="1">
         <v>4061022</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
     </row>
     <row r="33" ht="16.5" spans="1:9">
@@ -2604,22 +2659,22 @@
         <v>9</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="E33" s="1">
         <v>4061022</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
     </row>
     <row r="34" ht="16.5" spans="1:9">
@@ -2634,22 +2689,22 @@
         <v>10</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="E34" s="1">
         <v>4061022</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
     </row>
     <row r="35" ht="16.5" spans="1:9">
@@ -2664,22 +2719,22 @@
         <v>1</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="E35" s="3">
         <v>4061023</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="36" ht="16.5" spans="1:9">
@@ -2694,22 +2749,22 @@
         <v>2</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="E36" s="3">
         <v>4061023</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="37" ht="16.5" spans="1:9">
@@ -2724,22 +2779,22 @@
         <v>3</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="E37" s="3">
         <v>4061023</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="38" ht="16.5" spans="1:9">
@@ -2754,22 +2809,22 @@
         <v>4</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="E38" s="3">
         <v>4061023</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="39" ht="16.5" spans="1:9">
@@ -2784,22 +2839,22 @@
         <v>5</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="E39" s="3">
         <v>4061023</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="40" ht="16.5" spans="1:9">
@@ -2814,22 +2869,22 @@
         <v>6</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="E40" s="3">
         <v>4061023</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="41" ht="16.5" spans="1:9">
@@ -2844,22 +2899,22 @@
         <v>7</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="E41" s="3">
         <v>4061023</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
     </row>
     <row r="42" ht="16.5" spans="1:9">
@@ -2874,22 +2929,22 @@
         <v>8</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="E42" s="3">
         <v>4061023</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
     </row>
     <row r="43" ht="16.5" spans="1:9">
@@ -2904,22 +2959,22 @@
         <v>9</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="E43" s="3">
         <v>4061023</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
     </row>
     <row r="44" ht="16.5" spans="1:9">
@@ -2934,22 +2989,22 @@
         <v>10</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="E44" s="3">
         <v>4061023</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
     </row>
     <row r="45" ht="16.5" spans="1:9">
@@ -2964,22 +3019,22 @@
         <v>1</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="E45" s="1">
         <v>4061024</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I45" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="46" ht="16.5" spans="1:9">
@@ -2994,22 +3049,22 @@
         <v>2</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="E46" s="1">
         <v>4061024</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I46" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="47" ht="16.5" spans="1:9">
@@ -3024,22 +3079,22 @@
         <v>3</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="E47" s="1">
         <v>4061024</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="I47" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="48" ht="16.5" spans="1:9">
@@ -3054,22 +3109,22 @@
         <v>4</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="E48" s="1">
         <v>4061024</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I48" s="1" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="49" ht="16.5" spans="1:9">
@@ -3084,22 +3139,22 @@
         <v>5</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="E49" s="1">
         <v>4061024</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I49" s="1" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="50" ht="16.5" spans="1:9">
@@ -3114,22 +3169,22 @@
         <v>6</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="E50" s="1">
         <v>4061024</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="I50" s="1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="51" ht="16.5" spans="1:9">
@@ -3144,22 +3199,22 @@
         <v>7</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="E51" s="1">
         <v>4061024</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="I51" s="1" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
     </row>
     <row r="52" ht="16.5" spans="1:9">
@@ -3174,22 +3229,22 @@
         <v>8</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="E52" s="1">
         <v>4061024</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="I52" s="1" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
     </row>
     <row r="53" ht="16.5" spans="1:9">
@@ -3204,22 +3259,22 @@
         <v>9</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="E53" s="1">
         <v>4061024</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="I53" s="1" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
     </row>
     <row r="54" ht="16.5" spans="1:9">
@@ -3234,22 +3289,22 @@
         <v>10</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="E54" s="1">
         <v>4061024</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="I54" s="1" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
     </row>
     <row r="55" ht="16.5" spans="1:9">
@@ -3264,19 +3319,19 @@
         <v>1</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="E55" s="3">
         <v>4061025</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I55" s="3"/>
     </row>
@@ -3292,19 +3347,19 @@
         <v>2</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="E56" s="3">
         <v>4061025</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="G56" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I56" s="3"/>
     </row>
@@ -3320,19 +3375,19 @@
         <v>3</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="E57" s="3">
         <v>4061025</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="G57" s="3" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="I57" s="3"/>
     </row>
@@ -3348,19 +3403,19 @@
         <v>4</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="E58" s="3">
         <v>4061025</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I58" s="3"/>
     </row>
@@ -3376,19 +3431,19 @@
         <v>5</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="E59" s="3">
         <v>4061025</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="G59" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I59" s="3"/>
     </row>
@@ -3404,19 +3459,19 @@
         <v>6</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="E60" s="3">
         <v>4061025</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="I60" s="3"/>
     </row>
@@ -3432,19 +3487,19 @@
         <v>7</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="E61" s="3">
         <v>4061025</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="G61" s="3" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="I61" s="3"/>
     </row>
@@ -3460,19 +3515,19 @@
         <v>8</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="E62" s="3">
         <v>4061025</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="G62" s="3" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="I62" s="3"/>
     </row>
@@ -3488,19 +3543,19 @@
         <v>9</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="E63" s="3">
         <v>4061025</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="G63" s="3" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="I63" s="3"/>
     </row>
@@ -3516,19 +3571,19 @@
         <v>10</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="E64" s="3">
         <v>4061025</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="G64" s="3" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="I64" s="3"/>
     </row>

--- a/hall/resources/sample/PassDetails.xlsx
+++ b/hall/resources/sample/PassDetails.xlsx
@@ -94,7 +94,7 @@
     <t>PremiumPaidRewards</t>
   </si>
   <si>
-    <t>12284_1</t>
+    <t>12228_1</t>
   </si>
   <si>
     <t>签到1天</t>
@@ -109,7 +109,7 @@
     <t>1130002_1</t>
   </si>
   <si>
-    <t>12284_2</t>
+    <t>12228_2</t>
   </si>
   <si>
     <t>签到2天</t>
@@ -124,7 +124,7 @@
     <t>1130002_2</t>
   </si>
   <si>
-    <t>12284_3</t>
+    <t>12228_3</t>
   </si>
   <si>
     <t>签到3天</t>
@@ -139,7 +139,7 @@
     <t>1130002_3</t>
   </si>
   <si>
-    <t>12284_4</t>
+    <t>12228_4</t>
   </si>
   <si>
     <t>签到4天</t>
@@ -154,7 +154,7 @@
     <t>1130002_4</t>
   </si>
   <si>
-    <t>12284_5</t>
+    <t>12228_5</t>
   </si>
   <si>
     <t>签到5天</t>
@@ -169,7 +169,7 @@
     <t>1130002_5</t>
   </si>
   <si>
-    <t>12284_6</t>
+    <t>12228_6</t>
   </si>
   <si>
     <t>签到6天</t>
@@ -184,7 +184,7 @@
     <t>1130002_6</t>
   </si>
   <si>
-    <t>12284_7</t>
+    <t>12228_7</t>
   </si>
   <si>
     <t>签到7天</t>
@@ -199,7 +199,7 @@
     <t>1130002_7</t>
   </si>
   <si>
-    <t>12284_8</t>
+    <t>12228_8</t>
   </si>
   <si>
     <t>签到8天</t>
@@ -214,7 +214,7 @@
     <t>1130002_8</t>
   </si>
   <si>
-    <t>12284_9</t>
+    <t>12228_9</t>
   </si>
   <si>
     <t>签到9天</t>
@@ -229,7 +229,7 @@
     <t>1130002_9</t>
   </si>
   <si>
-    <t>12284_10</t>
+    <t>12228_10</t>
   </si>
   <si>
     <t>签到10天</t>
@@ -244,301 +244,301 @@
     <t>1130002_10</t>
   </si>
   <si>
-    <t>12607_5</t>
+    <t>12607_103800_5</t>
   </si>
   <si>
     <t>匹配5次</t>
   </si>
   <si>
-    <t>12607_10</t>
+    <t>12607_103800_10</t>
   </si>
   <si>
     <t>匹配10次</t>
   </si>
   <si>
-    <t>12607_15</t>
+    <t>12607_103800_15</t>
   </si>
   <si>
     <t>匹配15次</t>
   </si>
   <si>
-    <t>12607_20</t>
+    <t>12607_103800_20</t>
   </si>
   <si>
     <t>匹配20次</t>
   </si>
   <si>
-    <t>12607_25</t>
+    <t>12607_103800_25</t>
   </si>
   <si>
     <t>匹配25次</t>
   </si>
   <si>
-    <t>12607_30</t>
+    <t>12607_103800_30</t>
   </si>
   <si>
     <t>匹配30次</t>
   </si>
   <si>
-    <t>12607_35</t>
+    <t>12607_103800_35</t>
   </si>
   <si>
     <t>匹配35次</t>
   </si>
   <si>
-    <t>12607_40</t>
+    <t>12607_103800_40</t>
   </si>
   <si>
     <t>匹配40次</t>
   </si>
   <si>
-    <t>12607_45</t>
+    <t>12607_103800_45</t>
   </si>
   <si>
     <t>匹配45次</t>
   </si>
   <si>
-    <t>12607_50</t>
+    <t>12607_103800_50</t>
   </si>
   <si>
     <t>匹配50次</t>
   </si>
   <si>
-    <t>12608_2</t>
+    <t>12608_103800_2</t>
   </si>
   <si>
     <t>累计掉落宝石2次</t>
   </si>
   <si>
-    <t>12608_5</t>
+    <t>12608_103800_5</t>
   </si>
   <si>
     <t>累计掉落宝石5次</t>
   </si>
   <si>
-    <t>12608_8</t>
+    <t>12608_103800_8</t>
   </si>
   <si>
     <t>累计掉落宝石8次</t>
   </si>
   <si>
-    <t>12608_10</t>
+    <t>12608_103800_10</t>
   </si>
   <si>
     <t>累计掉落宝石10次</t>
   </si>
   <si>
-    <t>12608_15</t>
+    <t>12608_103800_15</t>
   </si>
   <si>
     <t>累计掉落宝石15次</t>
   </si>
   <si>
-    <t>12608_20</t>
+    <t>12608_103800_20</t>
   </si>
   <si>
     <t>累计掉落宝石20次</t>
   </si>
   <si>
-    <t>12608_25</t>
+    <t>12608_103800_25</t>
   </si>
   <si>
     <t>累计掉落宝石25次</t>
   </si>
   <si>
-    <t>12608_30</t>
+    <t>12608_103800_30</t>
   </si>
   <si>
     <t>累计掉落宝石30次</t>
   </si>
   <si>
-    <t>12608_40</t>
+    <t>12608_103800_40</t>
   </si>
   <si>
     <t>累计掉落宝石40次</t>
   </si>
   <si>
-    <t>12608_50</t>
+    <t>12608_103800_50</t>
   </si>
   <si>
     <t>累计掉落宝石50次</t>
   </si>
   <si>
-    <t>12610_0_100_1960000_10</t>
+    <t>12610_103800_100_10</t>
   </si>
   <si>
     <t>slot游戏下注10次</t>
   </si>
   <si>
-    <t>12610_0_100_1960000_20</t>
+    <t>12610_103800_100_20</t>
   </si>
   <si>
     <t>slot游戏下注20次</t>
   </si>
   <si>
-    <t>12610_0_100_1960000_30</t>
+    <t>12610_103800_100_30</t>
   </si>
   <si>
     <t>slot游戏下注30次</t>
   </si>
   <si>
-    <t>12610_0_100_1960000_40</t>
+    <t>12610_103800_100_40</t>
   </si>
   <si>
     <t>slot游戏下注40次</t>
   </si>
   <si>
-    <t>12610_0_100_1960000_50</t>
+    <t>12610_103800_100_50</t>
   </si>
   <si>
     <t>slot游戏下注50次</t>
   </si>
   <si>
-    <t>12610_0_100_1960000_60</t>
+    <t>12610_103800_100_60</t>
   </si>
   <si>
     <t>slot游戏下注60次</t>
   </si>
   <si>
-    <t>12610_0_100_1960000_70</t>
+    <t>12610_103800_100_70</t>
   </si>
   <si>
     <t>slot游戏下注70次</t>
   </si>
   <si>
-    <t>12610_0_100_1960000_80</t>
+    <t>12610_103800_100_80</t>
   </si>
   <si>
     <t>slot游戏下注80次</t>
   </si>
   <si>
-    <t>12610_0_100_1960000_90</t>
+    <t>12610_103800_100_90</t>
   </si>
   <si>
     <t>slot游戏下注90次</t>
   </si>
   <si>
-    <t>12610_0_100_1960000_100</t>
+    <t>12610_103800_100_100</t>
   </si>
   <si>
     <t>slot游戏下注100次</t>
   </si>
   <si>
-    <t>12609_0_100_1960000_100000</t>
+    <t>12609_103800_100_100000</t>
   </si>
   <si>
     <t>累计获取赛季币100000</t>
   </si>
   <si>
-    <t>12609_0_100_1960000_200000</t>
+    <t>12609_103800_100_200000</t>
   </si>
   <si>
     <t>累计获取赛季币200000</t>
   </si>
   <si>
-    <t>12609_0_100_1960000_300000</t>
+    <t>12609_103800_100_300000</t>
   </si>
   <si>
     <t>累计获取赛季币300000</t>
   </si>
   <si>
-    <t>12609_0_100_1960000_400000</t>
+    <t>12609_103800_100_400000</t>
   </si>
   <si>
     <t>累计获取赛季币400000</t>
   </si>
   <si>
-    <t>12609_0_100_1960000_500000</t>
+    <t>12609_103800_100_500000</t>
   </si>
   <si>
     <t>累计获取赛季币500000</t>
   </si>
   <si>
-    <t>12609_0_100_1960000_600000</t>
+    <t>12609_103800_100_600000</t>
   </si>
   <si>
     <t>累计获取赛季币600000</t>
   </si>
   <si>
-    <t>12609_0_100_1960000_700000</t>
+    <t>12609_103800_100_700000</t>
   </si>
   <si>
     <t>累计获取赛季币700000</t>
   </si>
   <si>
-    <t>12609_0_100_1960000_800000</t>
+    <t>12609_103800_100_800000</t>
   </si>
   <si>
     <t>累计获取赛季币800000</t>
   </si>
   <si>
-    <t>12609_0_100_1960000_900000</t>
+    <t>12609_103800_100_900000</t>
   </si>
   <si>
     <t>累计获取赛季币900000</t>
   </si>
   <si>
-    <t>12609_0_100_1960000_1000000</t>
+    <t>12609_103800_100_1000000</t>
   </si>
   <si>
     <t>累计获取赛季币1000000</t>
   </si>
   <si>
-    <t>1_5</t>
+    <t>12229_5</t>
   </si>
   <si>
     <t>用户等级达到5级</t>
   </si>
   <si>
-    <t>1_10</t>
+    <t>12229_10</t>
   </si>
   <si>
     <t>用户等级达到10级</t>
   </si>
   <si>
-    <t>1_15</t>
+    <t>12229_15</t>
   </si>
   <si>
     <t>用户等级达到15级</t>
   </si>
   <si>
-    <t>1_20</t>
+    <t>12229_20</t>
   </si>
   <si>
     <t>用户等级达到20级</t>
   </si>
   <si>
-    <t>1_25</t>
+    <t>12229_25</t>
   </si>
   <si>
     <t>用户等级达到25级</t>
   </si>
   <si>
-    <t>1_30</t>
+    <t>12229_30</t>
   </si>
   <si>
     <t>用户等级达到30级</t>
   </si>
   <si>
-    <t>1_35</t>
+    <t>12229_35</t>
   </si>
   <si>
     <t>用户等级达到35级</t>
   </si>
   <si>
-    <t>1_40</t>
+    <t>12229_40</t>
   </si>
   <si>
     <t>用户等级达到40级</t>
   </si>
   <si>
-    <t>1_45</t>
+    <t>12229_45</t>
   </si>
   <si>
     <t>用户等级达到45级</t>
   </si>
   <si>
-    <t>1_50</t>
+    <t>12229_50</t>
   </si>
   <si>
     <t>用户等级达到50级</t>

--- a/hall/resources/sample/PassDetails.xlsx
+++ b/hall/resources/sample/PassDetails.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="150">
   <si>
     <t>ID</t>
   </si>
@@ -482,66 +482,6 @@
   </si>
   <si>
     <t>累计获取赛季币1000000</t>
-  </si>
-  <si>
-    <t>12229_5</t>
-  </si>
-  <si>
-    <t>用户等级达到5级</t>
-  </si>
-  <si>
-    <t>12229_10</t>
-  </si>
-  <si>
-    <t>用户等级达到10级</t>
-  </si>
-  <si>
-    <t>12229_15</t>
-  </si>
-  <si>
-    <t>用户等级达到15级</t>
-  </si>
-  <si>
-    <t>12229_20</t>
-  </si>
-  <si>
-    <t>用户等级达到20级</t>
-  </si>
-  <si>
-    <t>12229_25</t>
-  </si>
-  <si>
-    <t>用户等级达到25级</t>
-  </si>
-  <si>
-    <t>12229_30</t>
-  </si>
-  <si>
-    <t>用户等级达到30级</t>
-  </si>
-  <si>
-    <t>12229_35</t>
-  </si>
-  <si>
-    <t>用户等级达到35级</t>
-  </si>
-  <si>
-    <t>12229_40</t>
-  </si>
-  <si>
-    <t>用户等级达到40级</t>
-  </si>
-  <si>
-    <t>12229_45</t>
-  </si>
-  <si>
-    <t>用户等级达到45级</t>
-  </si>
-  <si>
-    <t>12229_50</t>
-  </si>
-  <si>
-    <t>用户等级达到50级</t>
   </si>
 </sst>
 </file>
@@ -1713,7 +1653,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I64"/>
+  <dimension ref="A1:I54"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="4" max="4" width="18.875" customWidth="1"/>
@@ -3307,286 +3247,6 @@
         <v>69</v>
       </c>
     </row>
-    <row r="55" ht="16.5" spans="1:9">
-      <c r="A55" s="3">
-        <f t="shared" si="0"/>
-        <v>100601</v>
-      </c>
-      <c r="B55" s="3">
-        <v>1006</v>
-      </c>
-      <c r="C55" s="3">
-        <v>1</v>
-      </c>
-      <c r="D55" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="E55" s="3">
-        <v>4061025</v>
-      </c>
-      <c r="F55" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="G55" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H55" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="I55" s="3"/>
-    </row>
-    <row r="56" ht="16.5" spans="1:9">
-      <c r="A56" s="3">
-        <f t="shared" si="0"/>
-        <v>100602</v>
-      </c>
-      <c r="B56" s="3">
-        <v>1006</v>
-      </c>
-      <c r="C56" s="3">
-        <v>2</v>
-      </c>
-      <c r="D56" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="E56" s="3">
-        <v>4061025</v>
-      </c>
-      <c r="F56" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="G56" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="H56" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="I56" s="3"/>
-    </row>
-    <row r="57" ht="16.5" spans="1:9">
-      <c r="A57" s="3">
-        <f t="shared" si="0"/>
-        <v>100603</v>
-      </c>
-      <c r="B57" s="3">
-        <v>1006</v>
-      </c>
-      <c r="C57" s="3">
-        <v>3</v>
-      </c>
-      <c r="D57" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="E57" s="3">
-        <v>4061025</v>
-      </c>
-      <c r="F57" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="G57" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="H57" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="I57" s="3"/>
-    </row>
-    <row r="58" ht="16.5" spans="1:9">
-      <c r="A58" s="3">
-        <f t="shared" si="0"/>
-        <v>100604</v>
-      </c>
-      <c r="B58" s="3">
-        <v>1006</v>
-      </c>
-      <c r="C58" s="3">
-        <v>4</v>
-      </c>
-      <c r="D58" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="E58" s="3">
-        <v>4061025</v>
-      </c>
-      <c r="F58" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="G58" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="H58" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="I58" s="3"/>
-    </row>
-    <row r="59" ht="16.5" spans="1:9">
-      <c r="A59" s="3">
-        <f t="shared" si="0"/>
-        <v>100605</v>
-      </c>
-      <c r="B59" s="3">
-        <v>1006</v>
-      </c>
-      <c r="C59" s="3">
-        <v>5</v>
-      </c>
-      <c r="D59" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="E59" s="3">
-        <v>4061025</v>
-      </c>
-      <c r="F59" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="G59" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="H59" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="I59" s="3"/>
-    </row>
-    <row r="60" ht="16.5" spans="1:9">
-      <c r="A60" s="3">
-        <f t="shared" si="0"/>
-        <v>100606</v>
-      </c>
-      <c r="B60" s="3">
-        <v>1006</v>
-      </c>
-      <c r="C60" s="3">
-        <v>6</v>
-      </c>
-      <c r="D60" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="E60" s="3">
-        <v>4061025</v>
-      </c>
-      <c r="F60" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="G60" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="H60" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="I60" s="3"/>
-    </row>
-    <row r="61" ht="16.5" spans="1:9">
-      <c r="A61" s="3">
-        <f t="shared" si="0"/>
-        <v>100607</v>
-      </c>
-      <c r="B61" s="3">
-        <v>1006</v>
-      </c>
-      <c r="C61" s="3">
-        <v>7</v>
-      </c>
-      <c r="D61" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="E61" s="3">
-        <v>4061025</v>
-      </c>
-      <c r="F61" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="G61" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="H61" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="I61" s="3"/>
-    </row>
-    <row r="62" ht="16.5" spans="1:9">
-      <c r="A62" s="3">
-        <f t="shared" si="0"/>
-        <v>100608</v>
-      </c>
-      <c r="B62" s="3">
-        <v>1006</v>
-      </c>
-      <c r="C62" s="3">
-        <v>8</v>
-      </c>
-      <c r="D62" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="E62" s="3">
-        <v>4061025</v>
-      </c>
-      <c r="F62" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="G62" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="H62" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="I62" s="3"/>
-    </row>
-    <row r="63" ht="16.5" spans="1:9">
-      <c r="A63" s="3">
-        <f t="shared" si="0"/>
-        <v>100609</v>
-      </c>
-      <c r="B63" s="3">
-        <v>1006</v>
-      </c>
-      <c r="C63" s="3">
-        <v>9</v>
-      </c>
-      <c r="D63" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="E63" s="3">
-        <v>4061025</v>
-      </c>
-      <c r="F63" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="G63" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="H63" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="I63" s="3"/>
-    </row>
-    <row r="64" ht="16.5" spans="1:9">
-      <c r="A64" s="3">
-        <f t="shared" si="0"/>
-        <v>100610</v>
-      </c>
-      <c r="B64" s="3">
-        <v>1006</v>
-      </c>
-      <c r="C64" s="3">
-        <v>10</v>
-      </c>
-      <c r="D64" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="E64" s="3">
-        <v>4061025</v>
-      </c>
-      <c r="F64" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="G64" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="H64" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="I64" s="3"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
